--- a/Side Bar Files/GWD Data/PVC on Wall (Concealed) PRICE.xlsx
+++ b/Side Bar Files/GWD Data/PVC on Wall (Concealed) PRICE.xlsx
@@ -503,9 +503,15 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
+      <alignment/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -551,11 +557,15 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+      <alignment/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -958,7 +968,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5EB8FAE4-30D8-4753-B6B7-FD07A8F4B9A6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49958770-2319-4609-B228-543C8AFEB9A7}">
   <dimension ref="A1:G558"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>

--- a/Side Bar Files/GWD Data/PVC on Wall (Concealed) PRICE.xlsx
+++ b/Side Bar Files/GWD Data/PVC on Wall (Concealed) PRICE.xlsx
@@ -190,7 +190,7 @@
 (Adding 30% for fittings and wastage)</t>
   </si>
   <si>
-    <t>Providing and fixing PVC pipes, fittings including fixing the pipe with clamps at 1.00 m spacing. This includes jointing of pipes &amp; fittings with one step PVC solvent cement and testing of joints complete as per direction of Engineer-in-Charge. Concealed work, including cutting chases and making good the wall etc. 32 mm pipe 10Kgf/cm2  (50.18.8.4.1)</t>
+    <t>Providing and fixing PVC pipes, fittings including fixing the pipe with clamps at 1.00 m spacing. This includes jointing of pipes &amp; fittings with one step PVC solvent cement and testing of joints complete as per direction of Engineer-in-Charge. Concealed work, including cutting chases and making good the wall etc. 32 mm pipe 10Kgf/cm2 (50.18.8.4.1)</t>
   </si>
   <si>
     <t>MR44</t>
@@ -338,7 +338,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Cambria"/>
       <family val="2"/>
     </font>
     <font>
@@ -470,25 +470,11 @@
       </bottom>
     </border>
   </borders>
-  <cellStyleXfs count="20">
+  <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment/>
       <protection/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -587,11 +573,11 @@
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="15" builtinId="5"/>
-    <cellStyle name="Currency" xfId="16" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="17" builtinId="7"/>
-    <cellStyle name="Comma" xfId="18" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="19" builtinId="6"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="3" builtinId="7"/>
+    <cellStyle name="Comma" xfId="4" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="5" builtinId="6"/>
   </cellStyles>
   <colors>
     <indexedColors>
@@ -968,7 +954,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49958770-2319-4609-B228-543C8AFEB9A7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BF158AB-4F18-4147-A861-E1CEE75CBAA6}">
   <dimension ref="A1:G558"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>

--- a/Side Bar Files/GWD Data/PVC on Wall (Concealed) PRICE.xlsx
+++ b/Side Bar Files/GWD Data/PVC on Wall (Concealed) PRICE.xlsx
@@ -954,7 +954,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BF158AB-4F18-4147-A861-E1CEE75CBAA6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2855CF8B-08C2-4220-AC0D-2A6231CBBAA6}">
   <dimension ref="A1:G558"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>

--- a/Side Bar Files/GWD Data/PVC on Wall (Concealed) PRICE.xlsx
+++ b/Side Bar Files/GWD Data/PVC on Wall (Concealed) PRICE.xlsx
@@ -954,7 +954,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2855CF8B-08C2-4220-AC0D-2A6231CBBAA6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8356EDA4-D7CE-4E54-9C08-BDE1E11ABAA6}">
   <dimension ref="A1:G558"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>
